--- a/BOM/OpenHealthPod_BOM_v0.1.xlsx
+++ b/BOM/OpenHealthPod_BOM_v0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\manojMain\Github_LinkedIn\Hackzee\Hackster.io\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC661415-011D-435E-B182-ACE90F17D548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C8B55D-FA1E-4A5D-9F0B-600E79A33D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="58">
   <si>
     <t>SL No</t>
   </si>
@@ -107,9 +107,6 @@
     <t>Li-Po Battery</t>
   </si>
   <si>
-    <t>Rechargeable battery for wearable operation</t>
-  </si>
-  <si>
     <t>Custom UNO Q Shield PCB</t>
   </si>
   <si>
@@ -183,6 +180,21 @@
   </si>
   <si>
     <t>https://robu.in/product/ds18b20-water-proof-temperature-probe-black-1m-2/</t>
+  </si>
+  <si>
+    <t>Mounting Screws</t>
+  </si>
+  <si>
+    <t>For proper rigid Mounting</t>
+  </si>
+  <si>
+    <t>5V Fan</t>
+  </si>
+  <si>
+    <t>For enabling Proper Cooling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rechargeable battery for wearable operation </t>
   </si>
 </sst>
 </file>
@@ -752,7 +764,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E11" s="4">
         <v>1</v>
@@ -766,19 +778,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -786,13 +798,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>19</v>
@@ -806,19 +818,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="E14" s="4">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -826,19 +838,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="E15" s="4">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -846,19 +858,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="E16" s="4">
         <v>1</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -866,19 +878,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -886,19 +898,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="E18" s="4">
         <v>1</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -906,14 +918,14 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="E19" s="4">
         <v>1</v>
       </c>
@@ -922,19 +934,37 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="5">
+        <v>30</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1</v>
+      </c>
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -972,15 +1002,15 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -988,15 +1018,15 @@
         <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -1004,7 +1034,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
